--- a/site/exports/jlu-chemistry.xlsx
+++ b/site/exports/jlu-chemistry.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>化学学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>目录栏目、主页身份标签及旧文“至今”均不独立证实现时人事状态；不启用在岗导师快捷导航。；仅核原序前三，不代表院系全员、全职或完整履历。；论文仅核官网书目，未核出版社记录、DOI及全文。；院系行政父级和校区未核实，不推校级直属。；博士论文Advisor已按留存前2页影像与文本限定接受，不声称完整原PDF可独立复算或已读全文；其余审批姓名不推共同导师。；论文批准日期2005-08-17及封面December 2005均不是本包授位日期依据。；源站未单独读取导师个人主页；导师现职未知。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1490,8 +1544,378 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>原文仅1997获学士，入学年月及专业未披露。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>原文仅2000获硕士，入学年月及专业未披露。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>佐治亚理工学院</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>2005获博士来自吉林大学官网；论文封面/批准日期不作授位月日。；Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>postdoc</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>加州大学圣芭芭拉分校</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Historical 39-school classification uses exact matches in frozen baseline institution registry; unknown historical/abbreviated institution is not asserted non-985. Geography is institution-location normalization, not nationality or study location.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（event_kind）：postdoc</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>讲师、教授</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>上海大学</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>不拆出未经原文给出的职称分界。；任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学化学学院</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S12"/>
+  <autoFilter ref="A1:S18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1504,6 +1928,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1515,18 +1945,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="19.6" customWidth="1" min="2" max="2"/>
+    <col width="29.4" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1594,8 +2024,61 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Seth R. Marder</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>博士论文指导（Advisor，审批页原词）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；限定接受博士论文Advisor：仅留原第1、2页渲染、提取文本和派生2页PDF；完整181页原PDF字节未保存，原实体SHA256不能由留存资料独立复算，未读全文。其他四名审批人无Advisor标签，不作为导师。论文批准日及封面日期不作为授位日期；2005获博士仍只绑定吉林大学官网明确授位句。导师现职未知，导航关闭。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://repository.gatech.edu/server/api/core/bitstreams/2630a506-519e-44ee-bd9e-6e01124f3697/content</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1606,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1617,7 +2100,7 @@
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="60.2" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
-    <col width="58.8" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1909,8 +2392,112 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Triplet-Enhanced Photoiniferter Polymerization: Ultrafast, Oxygen-Tolerant, and Biocompatible Synthesis of Well-Defined Polymers under Visible Light</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源书目信息（bibliographic_details）：65(2), e22611</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Hydrophobic NIR photocatalysts for High-Throughput RAFT Aqueous Solution Polymerization: Achieving Ultrahigh Molecular Weights with 4-ppm Dye Colloids</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源书目信息（bibliographic_details）：65(4), e24395</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1920,6 +2507,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1931,14 +2522,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="25.2" customWidth="1" min="2" max="2"/>
-    <col width="62.99999999999999" customWidth="1" min="3" max="3"/>
-    <col width="25.2" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="61.59999999999999" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="44.8" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2128,13 +2719,127 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-jlu-anzesheng-s001-52dfb6e8c849</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/info/1048/9824.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:34:33.758770+00:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-jlu-anzesheng-s002-18b6fd105cc0</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://chem.jlu.edu.cn/szll/zzjg1/apypx1.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:32:32.443236+00:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>安泽胜</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-jlu-anzesheng-s003-3bb297a2d6e2</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://repository.gatech.edu/server/api/core/bitstreams/2630a506-519e-44ee-bd9e-6e01124f3697/content</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T10:36:46.866116+00:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>jlu</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
